--- a/jogos_2025-01-13.xlsx
+++ b/jogos_2025-01-13.xlsx
@@ -1030,16 +1030,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="M5" t="n">
-        <v>3.56</v>
+        <v>3.14</v>
       </c>
       <c r="N5" t="n">
-        <v>3.86</v>
+        <v>3.32</v>
       </c>
       <c r="O5" t="n">
         <v>2.88</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.5</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X5" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>['46', '60']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AI5" t="n">
         <v>1.67</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45670.54166666666</v>
@@ -1159,16 +1159,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1185,65 +1185,65 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>3.14</v>
+        <v>3.56</v>
       </c>
       <c r="N6" t="n">
-        <v>3.32</v>
+        <v>3.86</v>
       </c>
       <c r="O6" t="n">
         <v>2.88</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="X6" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['46', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" t="n">
         <v>1.67</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45670.54166666666</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.95</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>4.56</v>
+        <v>3.66</v>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>3.76</v>
       </c>
       <c r="O8" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>4.12</v>
+        <v>3.82</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['1', '44']</t>
+          <t>['7', '52', '78', '86', '90+3']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['14', '25', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.13</v>
+        <v>1.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.43</v>
+        <v>2.35</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45670.58333333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
@@ -1564,7 +1564,7 @@
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>5.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>4.56</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>3.9</v>
+        <v>4.12</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['14', '45+1', '88', '90+6']</t>
+          <t>['1', '44']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['30', '64', '81']</t>
+          <t>['14', '25', '60']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>2.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>1.13</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.3</v>
+        <v>1.43</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45670.58333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
         <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.41</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC10" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '45+1', '88', '90+6']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['8', '10', '22']</t>
+          <t>['30', '64', '81']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
         <v>1.73</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45670.58333333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1833,80 +1833,80 @@
         <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3.76</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
         <v>2.5</v>
       </c>
       <c r="P11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA11" t="n">
-        <v>3.06</v>
+        <v>3.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['27', '76']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.66</v>
       </c>
-      <c r="AD11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['7', '52', '78', '86', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AI11" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45670.58333333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.95</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.67</v>
-      </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['27', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '10', '22']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45670.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
         <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.05</v>
       </c>
-      <c r="M15" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
         <v>1.5</v>
@@ -2379,50 +2379,50 @@
         <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['22', '87']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45670.6875</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -2475,80 +2475,80 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="O16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.5</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="AD16" t="n">
         <v>1.5</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['22', '87']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ16" t="n">
         <v>3</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
         <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y17" t="n">
         <v>2.25</v>
       </c>
-      <c r="T17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.75</v>
-      </c>
       <c r="Z17" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['26']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>3</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45670.6875</v>
